--- a/artfynd/Lubbliden artfynd.xlsx
+++ b/artfynd/Lubbliden artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1989549</v>
+        <v>1987789</v>
       </c>
       <c r="B2" t="n">
-        <v>80083</v>
+        <v>80432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -706,17 +706,17 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>9 km S om Vargträsk, Ås lm</t>
+          <t>8 km SSV om Vargträsk, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>676102</v>
+        <v>675649</v>
       </c>
       <c r="R2" t="n">
-        <v>7116663</v>
+        <v>7117435</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2005-07-12</t>
+          <t>2005-06-11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2005-07-12</t>
+          <t>2005-06-11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -760,22 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Sveaskog Västerbotten</t>
+          <t>Daniella Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Sveaskog Västerbotten</t>
+          <t>Via Daniella Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126380535</v>
+        <v>1989549</v>
       </c>
       <c r="B3" t="n">
-        <v>57657</v>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,49 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Strand, Ås lm</t>
+          <t>9 km S om Vargträsk, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>676524</v>
+        <v>676102</v>
       </c>
       <c r="R3" t="n">
-        <v>7117516</v>
+        <v>7116663</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -849,17 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2005-07-12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Trummande hona</t>
+          <t>2005-07-12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,12 +857,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Daniella Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Carl Jansson, Rolf Nylinder</t>
+          <t>Via Daniella Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -889,7 +872,7 @@
         <v>1989541</v>
       </c>
       <c r="B4" t="n">
-        <v>80083</v>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -971,22 +954,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Sveaskog Västerbotten</t>
+          <t>Daniella Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Via Sveaskog Västerbotten</t>
+          <t>Via Daniella Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1989893</v>
+        <v>1989558</v>
       </c>
       <c r="B5" t="n">
-        <v>80083</v>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1018,13 +1001,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>676551</v>
+        <v>676167</v>
       </c>
       <c r="R5" t="n">
-        <v>7117277</v>
+        <v>7116770</v>
       </c>
       <c r="S5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1048,12 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2005-07-17</t>
+          <t>2005-07-13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2005-07-17</t>
+          <t>2005-07-13</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1068,22 +1051,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Sveaskog Västerbotten</t>
+          <t>Daniella Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Via Sveaskog Västerbotten</t>
+          <t>Via Daniella Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1989558</v>
+        <v>126380535</v>
       </c>
       <c r="B6" t="n">
-        <v>80083</v>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1091,37 +1074,49 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>9 km S om Vargträsk, Ås lm</t>
+          <t>Strand, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>676167</v>
+        <v>676524</v>
       </c>
       <c r="R6" t="n">
-        <v>7116770</v>
+        <v>7117516</v>
       </c>
       <c r="S6" t="n">
-        <v>250</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1145,12 +1140,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2005-07-13</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2005-07-13</t>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Trummande hona</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1165,12 +1165,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Sveaskog Västerbotten</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Via Sveaskog Västerbotten</t>
+          <t>Carl Jansson, Rolf Nylinder</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1180,7 +1180,7 @@
         <v>1989884</v>
       </c>
       <c r="B7" t="n">
-        <v>80083</v>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1262,22 +1262,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Sveaskog Västerbotten</t>
+          <t>Daniella Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Via Sveaskog Västerbotten</t>
+          <t>Via Daniella Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1987789</v>
+        <v>1989893</v>
       </c>
       <c r="B8" t="n">
-        <v>80083</v>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1305,17 +1305,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>8 km SSV om Vargträsk, Ås lm</t>
+          <t>9 km S om Vargträsk, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>675649</v>
+        <v>676551</v>
       </c>
       <c r="R8" t="n">
-        <v>7117435</v>
+        <v>7117277</v>
       </c>
       <c r="S8" t="n">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1339,12 +1339,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2005-06-11</t>
+          <t>2005-07-17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2005-06-11</t>
+          <t>2005-07-17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1359,12 +1359,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Sveaskog Västerbotten</t>
+          <t>Daniella Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Via Sveaskog Västerbotten</t>
+          <t>Via Daniella Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1374,7 +1374,7 @@
         <v>126380534</v>
       </c>
       <c r="B9" t="n">
-        <v>80083</v>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
